--- a/questionnaire/aifu_questionnaire_config_bilingual_full.xlsx
+++ b/questionnaire/aifu_questionnaire_config_bilingual_full.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="surveys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="blocks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="options" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="surveys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="blocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="questions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="options" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72,37 +72,37 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -466,8 +466,8 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="28"/>
+    <col customWidth="1" max="2" min="2" width="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,7 +483,6 @@
           <t>Ushbu fayl to'liq 2 tilli: o'zbek va rus.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -491,7 +490,6 @@
           <t>Bot `*_uz` va `*_ru` ustunlarga qarab savollarni chiqaradi.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -557,7 +555,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -570,15 +568,15 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="75" customWidth="1" min="7" max="7"/>
-    <col width="75" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col customWidth="1" max="1" min="1" width="18"/>
+    <col customWidth="1" max="2" min="2" width="28"/>
+    <col customWidth="1" max="3" min="3" width="28"/>
+    <col customWidth="1" max="4" min="4" width="28"/>
+    <col customWidth="1" max="5" min="5" width="28"/>
+    <col customWidth="1" max="6" min="6" width="10"/>
+    <col customWidth="1" max="7" min="7" width="75"/>
+    <col customWidth="1" max="8" min="8" width="75"/>
+    <col customWidth="1" max="9" min="9" width="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,7 +799,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -814,14 +812,14 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col customWidth="1" max="1" min="1" width="18"/>
+    <col customWidth="1" max="2" min="2" width="18"/>
+    <col customWidth="1" max="3" min="3" width="10"/>
+    <col customWidth="1" max="4" min="4" width="10"/>
+    <col customWidth="1" max="5" min="5" width="28"/>
+    <col customWidth="1" max="6" min="6" width="28"/>
+    <col customWidth="1" max="7" min="7" width="70"/>
+    <col customWidth="1" max="8" min="8" width="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1335,8 +1333,6 @@
           <t>ОЖИДАНИЯ СОТРУДНИКОВ И ПРЕДЛОЖЕНИЯ</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1407,8 +1403,6 @@
           <t>О ВАШЕМ РЕБЁНКЕ</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1479,8 +1473,6 @@
           <t>ОЖИДАНИЯ И ОПАСЕНИЯ</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1631,8 +1623,6 @@
           <t>ПРОФЕССИОНАЛЬНЫЕ ПЛАНЫ И ВЫБОР ВУЗА</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1667,7 +1657,7 @@
       <c r="H22" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1680,22 +1670,22 @@
   <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col customWidth="1" max="1" min="1" width="18"/>
+    <col customWidth="1" max="2" min="2" width="18"/>
+    <col customWidth="1" max="3" min="3" width="18"/>
+    <col customWidth="1" max="4" min="4" width="10"/>
+    <col customWidth="1" max="5" min="5" width="18"/>
+    <col customWidth="1" max="6" min="6" width="18"/>
+    <col customWidth="1" max="7" min="7" width="65"/>
+    <col customWidth="1" max="8" min="8" width="65"/>
+    <col customWidth="1" max="9" min="9" width="55"/>
+    <col customWidth="1" max="10" min="10" width="55"/>
+    <col customWidth="1" max="11" min="11" width="16"/>
+    <col customWidth="1" max="12" min="12" width="10"/>
+    <col customWidth="1" max="13" min="13" width="10"/>
+    <col customWidth="1" max="14" min="14" width="26"/>
+    <col customWidth="1" max="15" min="15" width="22"/>
+    <col customWidth="1" max="16" min="16" width="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2007,8 +1997,6 @@
           <t>Из какой вы области?</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2020,9 +2008,6 @@
       <c r="M5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -2251,8 +2236,6 @@
           <t>Каков ваш ежемесячный доход?</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2264,9 +2247,6 @@
       <c r="M9" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -2384,9 +2364,6 @@
       <c r="M11" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2504,9 +2481,6 @@
       <c r="M13" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2624,9 +2598,6 @@
       <c r="M15" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2744,9 +2715,6 @@
       <c r="M17" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2843,8 +2811,6 @@
           <t>Сколько времени в день вы проводите в социальных сетях?</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2856,9 +2822,6 @@
       <c r="M19" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2984,7 +2947,6 @@
       <c r="M21" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -3120,7 +3082,6 @@
       <c r="M23" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -3256,7 +3217,6 @@
       <c r="M25" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -3384,9 +3344,6 @@
       <c r="M27" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3504,9 +3461,6 @@
       <c r="M29" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3603,8 +3557,6 @@
           <t>Как часто вы пользуетесь общественным транспортом в неделю?</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3616,9 +3568,6 @@
       <c r="M31" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -3715,8 +3664,6 @@
           <t>Сколько вы тратите в месяц на образование и саморазвитие (курсы, книги и т.д.)?</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3728,9 +3675,6 @@
       <c r="M33" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3827,8 +3771,6 @@
           <t>Как давно вы знаете об AIFU?</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3840,9 +3782,6 @@
       <c r="M35" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3939,8 +3878,6 @@
           <t>Каким было ваше первое впечатление об AIFU?</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3952,9 +3889,6 @@
       <c r="M37" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -4043,8 +3977,6 @@
           <t>Порекомендовали бы вы AIFU своим друзьям или знакомым?</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4056,9 +3988,6 @@
       <c r="M39" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -4155,8 +4084,6 @@
           <t>Что вы планируете делать после окончания университета?</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4168,9 +4095,6 @@
       <c r="M41" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -4296,9 +4220,6 @@
       <c r="M43" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -4424,9 +4345,6 @@
       <c r="M45" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -4544,9 +4462,6 @@
       <c r="M47" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -4656,7 +4571,6 @@
       <c r="M49" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -4775,8 +4689,6 @@
           <t>Укажите ваш пол.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4788,9 +4700,6 @@
       <c r="M51" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -4900,7 +4809,6 @@
       <c r="M53" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -5019,8 +4927,6 @@
           <t>Ваше семейное положение?</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5032,9 +4938,6 @@
       <c r="M55" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -5123,8 +5026,6 @@
           <t>Ваш отдел или должность?</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5136,9 +5037,6 @@
       <c r="M57" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -5227,8 +5125,6 @@
           <t>Насколько вы довольны рабочей атмосферой?</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5240,9 +5136,6 @@
       <c r="M59" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -5360,9 +5253,6 @@
       <c r="M61" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5488,9 +5378,6 @@
       <c r="M63" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -5608,9 +5495,6 @@
       <c r="M65" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -5707,8 +5591,6 @@
           <t>Сколько времени в день вы проводите в социальных сетях?</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5720,9 +5602,6 @@
       <c r="M67" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -5848,7 +5727,6 @@
       <c r="M69" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -5984,7 +5862,6 @@
       <c r="M71" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -6120,7 +5997,6 @@
       <c r="M73" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -6248,9 +6124,6 @@
       <c r="M75" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -6368,9 +6241,6 @@
       <c r="M77" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -6467,8 +6337,6 @@
           <t>Как часто вы пользуетесь общественным транспортом в неделю?</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6480,9 +6348,6 @@
       <c r="M79" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -6579,8 +6444,6 @@
           <t>Сколько вы тратите в месяц на образование и саморазвитие (курсы, книги и т.д.)?</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6592,9 +6455,6 @@
       <c r="M81" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -6712,7 +6572,6 @@
       <c r="M83" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -6832,7 +6691,6 @@
       <c r="M85" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -6951,8 +6809,6 @@
           <t>Укажите ваш пол.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6964,9 +6820,6 @@
       <c r="M87" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -7076,7 +6929,6 @@
       <c r="M89" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -7195,8 +7047,6 @@
           <t>Ваше семейное положение?</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -7208,9 +7058,6 @@
       <c r="M91" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -7299,8 +7146,6 @@
           <t>На каком курсе обучается ваш ребёнок в AIFU?</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -7312,9 +7157,6 @@
       <c r="M93" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -7403,8 +7245,6 @@
           <t>Откуда вы впервые узнали об AIFU?</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -7416,9 +7256,6 @@
       <c r="M95" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -7515,8 +7352,6 @@
           <t>Насколько вы довольны учебным процессом вашего ребёнка в AIFU?</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -7528,9 +7363,6 @@
       <c r="M97" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -7648,9 +7480,6 @@
       <c r="M99" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -7768,9 +7597,6 @@
       <c r="M101" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -7880,7 +7706,6 @@
       <c r="M103" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -8016,7 +7841,6 @@
       <c r="M105" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -8152,7 +7976,6 @@
       <c r="M107" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -8288,9 +8111,6 @@
       <c r="M109" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -8408,9 +8228,6 @@
       <c r="M111" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -8528,9 +8345,6 @@
       <c r="M113" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -8627,8 +8441,6 @@
           <t>Что для вас важнее всего при оценке стоимости обучения?</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -8640,9 +8452,6 @@
       <c r="M115" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -8752,7 +8561,6 @@
       <c r="M117" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -8871,8 +8679,6 @@
           <t>Укажите ваш пол.</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -8884,9 +8690,6 @@
       <c r="M119" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -8996,7 +8799,6 @@
       <c r="M121" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -9115,8 +8917,6 @@
           <t>Ваше семейное положение?</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -9128,9 +8928,6 @@
       <c r="M123" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -9240,9 +9037,6 @@
       <c r="M125" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -9360,9 +9154,6 @@
       <c r="M127" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -9480,9 +9271,6 @@
       <c r="M129" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -9600,9 +9388,6 @@
       <c r="M131" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -9720,9 +9505,6 @@
       <c r="M133" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -9832,7 +9614,6 @@
       <c r="M135" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -9968,7 +9749,6 @@
       <c r="M137" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -10104,7 +9884,6 @@
       <c r="M139" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" s="4" t="inlineStr">
         <is>
           <t>Matn kiriting</t>
@@ -10240,9 +10019,6 @@
       <c r="M141" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -10360,9 +10136,6 @@
       <c r="M143" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -10472,9 +10245,6 @@
       <c r="M145" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -10563,8 +10333,6 @@
           <t>Каково ваше впечатление об AIFU на сегодняшний день?</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -10576,9 +10344,6 @@
       <c r="M147" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -10675,8 +10440,6 @@
           <t>Какие у вас планы после окончания университета?</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -10688,9 +10451,6 @@
       <c r="M149" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -10808,9 +10568,6 @@
       <c r="M151" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -10915,8 +10672,6 @@
           <t>Насколько уверенно вы смотрите в своё будущее?</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -10928,12 +10683,9 @@
       <c r="M153" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -10946,12 +10698,12 @@
   <dimension ref="A1:F869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col customWidth="1" max="1" min="1" width="18"/>
+    <col customWidth="1" max="2" min="2" width="18"/>
+    <col customWidth="1" max="3" min="3" width="12"/>
+    <col customWidth="1" max="4" min="4" width="12"/>
+    <col customWidth="1" max="5" min="5" width="45"/>
+    <col customWidth="1" max="6" min="6" width="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21477,12 +21229,12 @@
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
-          <t>Xushnudbek</t>
+          <t>Kun.uz</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>Xushnudbek</t>
+          <t>Kun.uz</t>
         </is>
       </c>
     </row>
@@ -21507,12 +21259,12 @@
       </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
-          <t>Kusherbayev</t>
+          <t>Daryo.uz</t>
         </is>
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>Kusherbayev</t>
+          <t>Daryo.uz</t>
         </is>
       </c>
     </row>
@@ -21537,12 +21289,12 @@
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>Alisher Sa'dullayev</t>
+          <t>Qalampir.uz</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>Alisher Sa'dullayev</t>
+          <t>Qalampir.uz</t>
         </is>
       </c>
     </row>
@@ -21567,12 +21319,12 @@
       </c>
       <c r="E354" s="6" t="inlineStr">
         <is>
-          <t>Xayrulla Hamidov</t>
+          <t>Gazeta.uz</t>
         </is>
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>Xayrulla Hamidov</t>
+          <t>Gazeta.uz</t>
         </is>
       </c>
     </row>
@@ -21597,12 +21349,12 @@
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
-          <t>Abdukarim Mirzayev</t>
+          <t>Vaqt.uz</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>Abdukarim Mirzayev</t>
+          <t>Vaqt.uz</t>
         </is>
       </c>
     </row>
@@ -21627,12 +21379,12 @@
       </c>
       <c r="E356" s="6" t="inlineStr">
         <is>
-          <t>Aziz Rahimov</t>
+          <t>Spot.uz</t>
         </is>
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>Aziz Rahimov</t>
+          <t>Spot.uz</t>
         </is>
       </c>
     </row>
@@ -21657,12 +21409,12 @@
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>Mirshakar Fayzullayev</t>
+          <t>Uznews</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>Mirshakar Fayzullayev</t>
+          <t>Uznews</t>
         </is>
       </c>
     </row>
@@ -21687,12 +21439,12 @@
       </c>
       <c r="E358" s="6" t="inlineStr">
         <is>
-          <t>Teacher A'zam</t>
+          <t>Repost.uz</t>
         </is>
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>Teacher A'zam</t>
+          <t>Repost.uz</t>
         </is>
       </c>
     </row>
@@ -21717,12 +21469,12 @@
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
-          <t>Timur Alihanov</t>
+          <t>Pressa.uz</t>
         </is>
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>Timur Alihanov</t>
+          <t>Pressa.uz</t>
         </is>
       </c>
     </row>
@@ -21747,12 +21499,12 @@
       </c>
       <c r="E360" s="6" t="inlineStr">
         <is>
-          <t>Makarenko</t>
+          <t>Sport yangiliklari</t>
         </is>
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>Makarenko</t>
+          <t>Спортивные новости</t>
         </is>
       </c>
     </row>
@@ -21777,12 +21529,12 @@
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
-          <t>Alter Ego</t>
+          <t>Hech birini kuzatmayman</t>
         </is>
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>Alter Ego</t>
+          <t>Не слежу ни за одним</t>
         </is>
       </c>
     </row>
@@ -21807,74 +21559,30 @@
       </c>
       <c r="E362" s="7" t="inlineStr">
         <is>
-          <t>Ingliz tili ustozlari</t>
+          <t>Boshqa (yozaman)</t>
         </is>
       </c>
       <c r="F362" s="7" t="inlineStr">
         <is>
-          <t>Преподаватели английского</t>
+          <t>Другое (напишу)</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="4" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B363" s="4" t="inlineStr">
-        <is>
-          <t>employee_q016</t>
-        </is>
-      </c>
-      <c r="C363" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D363" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E363" s="2" t="inlineStr">
-        <is>
-          <t>Hech kimni kuzatmayman</t>
-        </is>
-      </c>
-      <c r="F363" s="4" t="inlineStr">
-        <is>
-          <t>Ни за кем не слежу</t>
-        </is>
-      </c>
+      <c r="A363" s="4" t="n"/>
+      <c r="B363" s="4" t="n"/>
+      <c r="C363" s="9" t="n"/>
+      <c r="D363" s="4" t="n"/>
+      <c r="E363" s="2" t="n"/>
+      <c r="F363" s="4" t="n"/>
     </row>
     <row r="364">
-      <c r="A364" s="6" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B364" s="6" t="inlineStr">
-        <is>
-          <t>employee_q016</t>
-        </is>
-      </c>
-      <c r="C364" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D364" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E364" s="6" t="inlineStr">
-        <is>
-          <t>Boshqa (yozaman)</t>
-        </is>
-      </c>
-      <c r="F364" s="6" t="inlineStr">
-        <is>
-          <t>Другое (напишу)</t>
-        </is>
-      </c>
+      <c r="A364" s="6" t="n"/>
+      <c r="B364" s="6" t="n"/>
+      <c r="C364" s="8" t="n"/>
+      <c r="D364" s="6" t="n"/>
+      <c r="E364" s="6" t="n"/>
+      <c r="F364" s="6" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
@@ -22052,7 +21760,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>Aziz Rahimov</t>
+          <t>Muhammadali Eshonqulov</t>
         </is>
       </c>
     </row>
@@ -22082,7 +21790,7 @@
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>Mirshakar Fayzullayev</t>
+          <t>Aziz Rahimov</t>
         </is>
       </c>
     </row>
@@ -22112,7 +21820,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>Teacher A'zam</t>
+          <t>Преподаватели английского</t>
         </is>
       </c>
     </row>
@@ -22142,7 +21850,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>Timur Alihanov</t>
+          <t>Mirshakar Fayzullayev</t>
         </is>
       </c>
     </row>
@@ -22172,7 +21880,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>Makarenko</t>
+          <t>Teacher A'zam</t>
         </is>
       </c>
     </row>
@@ -22202,7 +21910,7 @@
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>Alter Ego</t>
+          <t>Timur Alihanov</t>
         </is>
       </c>
     </row>
@@ -22232,7 +21940,7 @@
       </c>
       <c r="F376" s="7" t="inlineStr">
         <is>
-          <t>Преподаватели английского</t>
+          <t>Ни за кем не слежу</t>
         </is>
       </c>
     </row>
@@ -22262,39 +21970,17 @@
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>Ни за кем не слежу</t>
+          <t>Другое (напишу)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="6" t="inlineStr">
-        <is>
-          <t>employee</t>
-        </is>
-      </c>
-      <c r="B378" s="6" t="inlineStr">
-        <is>
-          <t>employee_q017</t>
-        </is>
-      </c>
-      <c r="C378" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D378" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E378" s="6" t="inlineStr">
-        <is>
-          <t>Другое (напишу)</t>
-        </is>
-      </c>
-      <c r="F378" s="6" t="inlineStr">
-        <is>
-          <t>Другое (напишу)</t>
-        </is>
-      </c>
+      <c r="A378" s="6" t="n"/>
+      <c r="B378" s="6" t="n"/>
+      <c r="C378" s="8" t="n"/>
+      <c r="D378" s="6" t="n"/>
+      <c r="E378" s="6" t="n"/>
+      <c r="F378" s="6" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
@@ -37027,6 +36713,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/questionnaire/aifu_questionnaire_config_bilingual_full.xlsx
+++ b/questionnaire/aifu_questionnaire_config_bilingual_full.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TALABALAR SOROVNOMASI (Bakalavr va Magistr)</t>
+          <t>TALABALAR SO'ROVNOMASI (Bakalavr va Magistr)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XODIMLAR SOROVNOMASI</t>
+          <t>XODIMLAR SO'ROVNOMASI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OTA-ONALAR SOROVNOMASI</t>
+          <t>OTA-ONALAR SO'ROVNOMASI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ABITURIYENTLAR SOROVNOMASI</t>
+          <t>ABITURIYENTLAR SO'ROVNOMASI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1123,8 +1123,6 @@
           <t>ОЖИДАНИЯ СОТРУДНИКОВ И ПРЕДЛОЖЕНИЯ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1195,8 +1193,6 @@
           <t>О ВАШЕМ РЕБЁНКЕ</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1267,8 +1263,6 @@
           <t>ОЖИДАНИЯ И ОПАСЕНИЯ</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1419,8 +1413,6 @@
           <t>ПРОФЕССИОНАЛЬНЫЕ ПЛАНЫ И ВЫБОР УНИВЕРСИТЕТА</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1451,8 +1443,6 @@
           <t>ОЖИДАНИЯ И ТРЕВОГИ</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1611,8 +1601,6 @@
           <t>^\d+$</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1649,8 +1637,6 @@
           <t>Выберите ваш пол.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -1662,9 +1648,6 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1701,8 +1684,6 @@
           <t>Из какой вы области?</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -1714,9 +1695,6 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1774,9 +1752,6 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1813,8 +1788,6 @@
           <t>В каком диапазоне находится ваш ежемесячный доход?</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -1826,9 +1799,6 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1886,9 +1856,6 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1946,9 +1913,6 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2006,9 +1970,6 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2066,9 +2027,6 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2126,9 +2084,6 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2186,9 +2141,6 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2246,9 +2198,6 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2306,9 +2255,6 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2366,9 +2312,6 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2426,9 +2369,6 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2486,9 +2426,6 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2525,8 +2462,6 @@
           <t>Сколько раз в неделю вы в среднем пользуетесь общественным транспортом?</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2538,9 +2473,6 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2598,9 +2530,6 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2637,8 +2566,6 @@
           <t>Сколько денег в месяц вы тратите на образование и развитие (курсы, книги и т.д.)?</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2650,9 +2577,6 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2710,9 +2634,6 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2770,9 +2691,6 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2830,9 +2748,6 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2869,8 +2784,6 @@
           <t>Порекомендуете ли вы AIFU своим друзьям или знакомым?</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2882,9 +2795,6 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2942,9 +2852,6 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2981,8 +2888,6 @@
           <t>Каковы ваши планы после окончания университета?</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -2994,9 +2899,6 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3054,9 +2956,6 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3114,9 +3013,6 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3174,9 +3070,6 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3234,9 +3127,6 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3299,8 +3189,6 @@
           <t>^\d+$</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3337,8 +3225,6 @@
           <t>Выберите ваш пол.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3350,9 +3236,6 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3389,8 +3272,6 @@
           <t>Из какой вы области?</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3402,9 +3283,6 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3462,9 +3340,6 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3501,8 +3376,6 @@
           <t>В каком диапазоне находится ваш ежемесячный доход?</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3514,9 +3387,6 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3553,8 +3423,6 @@
           <t>Ваш отдел или должность?</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -3566,9 +3434,6 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3626,9 +3491,6 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3686,9 +3548,6 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3746,9 +3605,6 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3806,9 +3662,6 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3866,9 +3719,6 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3926,9 +3776,6 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3986,9 +3833,6 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4046,9 +3890,6 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4106,9 +3947,6 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4166,9 +4004,6 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4226,9 +4061,6 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4286,9 +4118,6 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4346,9 +4175,6 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4406,9 +4232,6 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4466,9 +4289,6 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4505,8 +4325,6 @@
           <t>Сколько раз в неделю вы в среднем пользуетесь общественным транспортом?</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4518,9 +4336,6 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4578,9 +4393,6 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4617,8 +4429,6 @@
           <t>Сколько денег в месяц вы тратите на образование и развитие (курсы, книги и т.д.)?</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4630,9 +4440,6 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4690,9 +4497,6 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4750,9 +4554,6 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4789,8 +4590,6 @@
           <t>Порекомендуете ли вы AIFU своим друзьям в качестве места работы?</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4802,9 +4601,6 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4867,8 +4663,6 @@
           <t>^\d+$</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4905,8 +4699,6 @@
           <t>Выберите ваш пол.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4918,9 +4710,6 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4957,8 +4746,6 @@
           <t>Из какой вы области?</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -4970,9 +4757,6 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5030,9 +4814,6 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5069,8 +4850,6 @@
           <t>В каком диапазоне находится ваш ежемесячный доход?</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5082,9 +4861,6 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5121,8 +4897,6 @@
           <t>На каком курсе обучается ваш ребёнок в AIFU?</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5134,9 +4908,6 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5173,8 +4944,6 @@
           <t>Кто принял решение о поступлении вашего ребёнка в AIFU?</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5186,9 +4955,6 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5225,8 +4991,6 @@
           <t>Где вы впервые услышали об AIFU?</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -5238,9 +5002,6 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5298,9 +5059,6 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5358,9 +5116,6 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5418,9 +5173,6 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5478,9 +5230,6 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5538,9 +5287,6 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5598,9 +5344,6 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5658,9 +5401,6 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5718,9 +5458,6 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5778,9 +5515,6 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5838,9 +5572,6 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5898,9 +5629,6 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5958,9 +5686,6 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6018,9 +5743,6 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6078,9 +5800,6 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6117,8 +5836,6 @@
           <t>Какой критерий наиболее важен при оценке стоимости обучения?</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6130,9 +5847,6 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6169,8 +5883,6 @@
           <t>Порекомендуете ли вы AIFU другим родителям?</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6182,9 +5894,6 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6247,8 +5956,6 @@
           <t>^\d+$</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6285,8 +5992,6 @@
           <t>Выберите ваш пол.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6298,9 +6003,6 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6337,8 +6039,6 @@
           <t>Из какой вы области?</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6350,9 +6050,6 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6410,9 +6107,6 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6449,8 +6143,6 @@
           <t>В каком диапазоне находится ваш ежемесячный доход?</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -6462,9 +6154,6 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6522,9 +6211,6 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6582,9 +6268,6 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6642,9 +6325,6 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6702,9 +6382,6 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6762,9 +6439,6 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6822,9 +6496,6 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6882,9 +6553,6 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6942,9 +6610,6 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7002,9 +6667,6 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7062,9 +6724,6 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7122,9 +6781,6 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7182,9 +6838,6 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7242,9 +6895,6 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7281,8 +6931,6 @@
           <t>В каком направлении вы планируете учиться?</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -7294,9 +6942,6 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7354,9 +6999,6 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7393,8 +7035,6 @@
           <t>Каковы ваши планы после окончания университета?</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>single_choice</t>
@@ -7406,9 +7046,6 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7466,9 +7103,6 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7526,9 +7160,6 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7586,9 +7217,6 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
